--- a/output/laminas_provinciales/prov_i_peringr_median_a_2024_valparaiso.xlsx
+++ b/output/laminas_provinciales/prov_i_peringr_median_a_2024_valparaiso.xlsx
@@ -86,7 +86,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 11:17</t>
+    <t xml:space="preserve">2026-09-09 22:16</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/laminas_provinciales/prov_i_peringr_median_a_2024_valparaiso.xlsx
+++ b/output/laminas_provinciales/prov_i_peringr_median_a_2024_valparaiso.xlsx
@@ -86,7 +86,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:16</t>
+    <t xml:space="preserve">2026-09-17 13:43</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -1243,18 +1243,18 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>12.23</v>
+        <v>13.07</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>13.65</v>
+        <v>12.23</v>
       </c>
     </row>
     <row r="4">
@@ -1291,10 +1291,10 @@
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>13.07</v>
+        <v>13.65</v>
       </c>
     </row>
   </sheetData>
@@ -1327,101 +1327,101 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>35</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>10.47</v>
+        <v>14.1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>8.24</v>
+        <v>13.64</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>6.49</v>
+        <v>13.07</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>35</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>13.39</v>
+        <v>10.47</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>12.52</v>
+        <v>8.24</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>12.23</v>
+        <v>6.49</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>35</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>14.85</v>
+        <v>13.39</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>14.36</v>
+        <v>12.52</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>13.65</v>
+        <v>12.23</v>
       </c>
     </row>
     <row r="11">
@@ -1558,35 +1558,35 @@
     </row>
     <row r="23">
       <c r="A23" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>35</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>14.1</v>
+        <v>14.85</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>36</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>13.64</v>
+        <v>14.36</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>13.07</v>
+        <v>13.65</v>
       </c>
     </row>
     <row r="26">

--- a/output/laminas_provinciales/prov_i_peringr_median_a_2024_valparaiso.xlsx
+++ b/output/laminas_provinciales/prov_i_peringr_median_a_2024_valparaiso.xlsx
@@ -86,7 +86,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 13:43</t>
+    <t xml:space="preserve">2026-09-25 21:38</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -542,7 +542,7 @@
         <v>-1.94</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-22.85</v>
+        <v>-22.86</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>9</v>
@@ -565,7 +565,7 @@
         <v>-1.56</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>-19.55</v>
+        <v>-19.6</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>9</v>
@@ -585,10 +585,10 @@
         <v>8.24</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>-1.75</v>
+        <v>-1.76</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-21.24</v>
+        <v>-21.31</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>9</v>
@@ -611,7 +611,7 @@
         <v>-0.49</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-2.89</v>
+        <v>-2.86</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>8</v>
@@ -634,7 +634,7 @@
         <v>-0.12</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-1.26</v>
+        <v>-1.29</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>8</v>
@@ -654,10 +654,10 @@
         <v>12.52</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-0.29</v>
+        <v>-0.3</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-2.32</v>
+        <v>-2.36</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>8</v>
@@ -680,7 +680,7 @@
         <v>-1.16</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-6.74</v>
+        <v>-6.73</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>7</v>
@@ -700,10 +700,10 @@
         <v>11.25</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>-1.38</v>
+        <v>-1.37</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-12.27</v>
+        <v>-12.21</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>7</v>
@@ -723,10 +723,10 @@
         <v>13.82</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>-1.31</v>
+        <v>-1.3</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-9.48</v>
+        <v>-9.43</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>7</v>
@@ -772,7 +772,7 @@
         <v>-0.93</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-8.58</v>
+        <v>-8.59</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>6</v>
@@ -795,7 +795,7 @@
         <v>-1.05</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-7.55</v>
+        <v>-7.56</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>6</v>
@@ -818,7 +818,7 @@
         <v>-0.81</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-4.72</v>
+        <v>-4.75</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>5</v>
@@ -841,7 +841,7 @@
         <v>-0.4</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-3.7</v>
+        <v>-3.71</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>5</v>
@@ -861,10 +861,10 @@
         <v>13.64</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>-0.57</v>
+        <v>-0.58</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-4.18</v>
+        <v>-4.23</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>5</v>
@@ -887,7 +887,7 @@
         <v>-0.82</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-4.61</v>
+        <v>-4.59</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>4</v>
@@ -910,7 +910,7 @@
         <v>-0.76</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-6.72</v>
+        <v>-6.68</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>4</v>
@@ -933,7 +933,7 @@
         <v>-0.79</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-5.59</v>
+        <v>-5.6</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>4</v>
@@ -953,10 +953,10 @@
         <v>17.75</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>-0.36</v>
+        <v>-0.37</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-2.03</v>
+        <v>-2.07</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>3</v>
@@ -976,10 +976,10 @@
         <v>11.64</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>-0.95</v>
+        <v>-0.96</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-8.16</v>
+        <v>-8.22</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>3</v>
@@ -1002,7 +1002,7 @@
         <v>-0.71</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-4.94</v>
+        <v>-4.93</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>3</v>
@@ -1025,7 +1025,7 @@
         <v>-1.72</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-7.7</v>
+        <v>-7.68</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>2</v>
@@ -1048,7 +1048,7 @@
         <v>-1.94</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-16.32</v>
+        <v>-16.31</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>2</v>
@@ -1068,10 +1068,10 @@
         <v>16.26</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>-1.9</v>
+        <v>-1.91</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-11.69</v>
+        <v>-11.72</v>
       </c>
       <c r="G25" s="2" t="n">
         <v>2</v>
@@ -1094,7 +1094,7 @@
         <v>-0.73</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-3.64</v>
+        <v>-3.63</v>
       </c>
       <c r="G26" s="2" t="n">
         <v>1</v>
@@ -1117,7 +1117,7 @@
         <v>-0.9</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-6.06</v>
+        <v>-6.07</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>1</v>

--- a/output/laminas_provinciales/prov_i_peringr_median_a_2024_valparaiso.xlsx
+++ b/output/laminas_provinciales/prov_i_peringr_median_a_2024_valparaiso.xlsx
@@ -67,7 +67,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 21:39</t>
+    <t xml:space="preserve">2026-10-05 07:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
